--- a/astrologija_biljke.xlsx
+++ b/astrologija_biljke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tankos_iva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744639E6-335C-4222-97C8-AAEE0631DA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3DF2FB-47F6-46BE-A189-7752E8CAAFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1642,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1650,186 +1650,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1848,186 +1848,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>354</v>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A3:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2046,186 +2046,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B16" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D16" s="12" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2244,186 +2244,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2442,186 +2442,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2640,186 +2640,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2838,186 +2838,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3036,186 +3036,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3234,186 +3234,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>288</v>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3432,186 +3432,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>324</v>
       </c>
     </row>

--- a/astrologija_biljke.xlsx
+++ b/astrologija_biljke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tankos_iva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3DF2FB-47F6-46BE-A189-7752E8CAAFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC319BE1-D6FF-4D1C-9B0E-FFE73748FE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2038,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A3:D16"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2046,186 +2046,186 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>53</v>
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>56</v>
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>59</v>
+      <c r="A7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>62</v>
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>65</v>
+      <c r="A9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>68</v>
+      <c r="A10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>71</v>
+      <c r="A11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>74</v>
+      <c r="A12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>77</v>
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>79</v>
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>85</v>
       </c>
     </row>
